--- a/output/pdf_financials_xlsx/XMF.A.xlsx
+++ b/output/pdf_financials_xlsx/XMF.A.xlsx
@@ -2125,40 +2125,40 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.959565</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>3.965263</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.777641</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>1.451667</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>2.050896</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>2.023802</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>7.757705</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.218015</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>1.130615</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.765833</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>3.455721</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.54239</v>
       </c>
     </row>
     <row r="35">
@@ -2211,40 +2211,40 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1.959565</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>3.965263</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.777641</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>1.451667</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>2.050896</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>2.023802</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>7.757705</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.218015</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>1.130615</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.765833</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>3.455721</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.54239</v>
       </c>
     </row>
     <row r="37">
@@ -2727,40 +2727,40 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>21.829261</v>
+        <v>19.869696</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>27.810007</v>
+        <v>23.844744</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>24.287359</v>
+        <v>22.509718</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>25.117669</v>
+        <v>23.666002</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>27.805396</v>
+        <v>25.7545</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>22.33287</v>
+        <v>20.309068</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>24.76727</v>
+        <v>17.009565</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>13.928867</v>
+        <v>13.710852</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>14.333542</v>
+        <v>13.202927</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>14.946263</v>
+        <v>14.18043</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>23.079199</v>
+        <v>19.623478</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>13.919078</v>
+        <v>13.376688</v>
       </c>
     </row>
     <row r="49">
@@ -6982,7 +6982,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -10890,7 +10890,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E59" s="5" t="n">

--- a/output/pdf_financials_xlsx/XMF.A.xlsx
+++ b/output/pdf_financials_xlsx/XMF.A.xlsx
@@ -712,40 +712,40 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.112526</v>
+        <v>0.133986</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.153674</v>
+        <v>0.177257</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.160693</v>
+        <v>0.184276</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.139815</v>
+        <v>0.163398</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.160962</v>
+        <v>0.184545</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.151183</v>
+        <v>0.174766</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.147153</v>
+        <v>0.170736</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.10417</v>
+        <v>0.127753</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.107555</v>
+        <v>0.12958</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.104848</v>
+        <v>0.119182</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.130306</v>
+        <v>0.144618</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.096439</v>
+        <v>0.110772</v>
       </c>
     </row>
     <row r="8">
@@ -5796,40 +5796,40 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>3.825149</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>1.27341</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>1.535752</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>1.267967</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>5.909546</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0</v>
+        <v>1.07038</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>9.079712000000001</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>0.564163</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>1.223936</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>0</v>
+        <v>-0.06218</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>0</v>
+        <v>2.966835</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>0</v>
+        <v>7.628125</v>
       </c>
     </row>
     <row r="116">
@@ -6510,55 +6510,35 @@
       <c r="C130" s="3" t="n">
         <v>1.959565</v>
       </c>
-      <c r="D130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D130" s="3" t="n">
+        <v>3.965263</v>
+      </c>
+      <c r="E130" s="3" t="n">
+        <v>1.777641</v>
+      </c>
+      <c r="F130" s="3" t="n">
+        <v>1.451667</v>
+      </c>
+      <c r="G130" s="3" t="n">
+        <v>2.050896</v>
+      </c>
+      <c r="H130" s="3" t="n">
+        <v>2.023802</v>
+      </c>
+      <c r="I130" s="3" t="n">
+        <v>0.072204</v>
+      </c>
+      <c r="J130" s="3" t="n">
+        <v>0.218015</v>
+      </c>
+      <c r="K130" s="3" t="n">
+        <v>1.130615</v>
+      </c>
+      <c r="L130" s="3" t="n">
+        <v>0.765833</v>
+      </c>
+      <c r="M130" s="3" t="n">
+        <v>3.455721</v>
       </c>
     </row>
     <row r="131">
@@ -6659,55 +6639,35 @@
       <c r="C133" s="3" t="n">
         <v>3.965263</v>
       </c>
-      <c r="D133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D133" s="3" t="n">
+        <v>1.777641</v>
+      </c>
+      <c r="E133" s="3" t="n">
+        <v>1.451667</v>
+      </c>
+      <c r="F133" s="3" t="n">
+        <v>2.050896</v>
+      </c>
+      <c r="G133" s="3" t="n">
+        <v>2.023802</v>
+      </c>
+      <c r="H133" s="3" t="n">
+        <v>7.757705</v>
+      </c>
+      <c r="I133" s="3" t="n">
+        <v>0.218015</v>
+      </c>
+      <c r="J133" s="3" t="n">
+        <v>1.130615</v>
+      </c>
+      <c r="K133" s="3" t="n">
+        <v>0.765833</v>
+      </c>
+      <c r="L133" s="3" t="n">
+        <v>3.455721</v>
+      </c>
+      <c r="M133" s="3" t="n">
+        <v>0.54239</v>
       </c>
     </row>
     <row r="134">
@@ -12710,7 +12670,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
           <t>-</t>
@@ -13296,7 +13260,11 @@
           <t>Cash at beginning of the year</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
           <t>-</t>
@@ -13370,7 +13338,11 @@
           <t>Cash at end of the year</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
           <t>-</t>
@@ -14338,7 +14310,11 @@
           <t>Cash at beginning of the year</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
           <t>-</t>
@@ -14398,7 +14374,11 @@
           <t>Cash at end of the year</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
           <t>-</t>
@@ -16194,7 +16174,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr"/>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
           <t>-</t>
@@ -19224,7 +19208,11 @@
           <t>Cash at beginning of the year</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr"/>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E174" t="inlineStr">
         <is>
           <t>-</t>
@@ -19298,7 +19286,11 @@
           <t>Cash at end of the year</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr"/>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E175" t="inlineStr">
         <is>
           <t>-</t>
@@ -19966,7 +19958,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr"/>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E184" s="5" t="n">
         <v>3.825149</v>
       </c>
@@ -21998,7 +21994,11 @@
           <t>Directors’ fees</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr"/>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E212" s="5" t="n">
         <v>0.02146</v>
       </c>
@@ -22578,7 +22578,11 @@
           <t>Distributions on Preferred shares</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr"/>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>PreferredStockDividends</t>
+        </is>
+      </c>
       <c r="E222" t="inlineStr">
         <is>
           <t>-</t>
@@ -23582,7 +23586,11 @@
           <t>Director’s fees</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr"/>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E236" t="inlineStr">
         <is>
           <t>-</t>
@@ -23714,7 +23722,11 @@
           <t>Distributions on Preferred shares</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr"/>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>PreferredStockDividends</t>
+        </is>
+      </c>
       <c r="E238" t="inlineStr">
         <is>
           <t>-</t>
@@ -24618,7 +24630,11 @@
           <t>Distributions on preferred shares</t>
         </is>
       </c>
-      <c r="D250" t="inlineStr"/>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>PreferredStockDividends</t>
+        </is>
+      </c>
       <c r="E250" t="inlineStr">
         <is>
           <t>-</t>
@@ -25218,7 +25234,11 @@
           <t>Net investment income before distributions on Preferred shares</t>
         </is>
       </c>
-      <c r="D258" t="inlineStr"/>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>PreferredStockDividends</t>
+        </is>
+      </c>
       <c r="E258" s="5" t="n">
         <v>0.280269</v>
       </c>
@@ -25292,7 +25312,11 @@
           <t>Distributions on Preferred shares (note 5 and 8)</t>
         </is>
       </c>
-      <c r="D259" t="inlineStr"/>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>PreferredStockDividends</t>
+        </is>
+      </c>
       <c r="E259" s="5" t="n">
         <v>-1.025677</v>
       </c>
